--- a/InputData/elec/DRC/Demand Response Capacity.xlsx
+++ b/InputData/elec/DRC/Demand Response Capacity.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/TARGET_eps-us-3.2.1/InputData/elec/DRC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF18D30-C872-8641-B28C-E82493455792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{EAF18D30-C872-8641-B28C-E82493455792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85781D6E-DF9F-47DE-9867-BAA8E93E065C}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="500" windowWidth="23960" windowHeight="12280" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="500" windowWidth="23960" windowHeight="12280" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Calculations" sheetId="4" r:id="rId2"/>
+    <sheet name="Data and Calculations" sheetId="4" r:id="rId2"/>
     <sheet name="Scaling Factors" sheetId="6" r:id="rId3"/>
     <sheet name="DRC-BDRC" sheetId="5" r:id="rId4"/>
     <sheet name="DRC-PADRC" sheetId="2" r:id="rId5"/>
+    <sheet name="DRC-ADRHpDRE" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,6 +35,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,96 +44,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+  <si>
+    <t>DRC BAU Demand Response Capacity</t>
+  </si>
+  <si>
+    <t>DRC Potential Additional Demand Response Capacity</t>
+  </si>
+  <si>
+    <t>DRC Hours of DR Average Utility May Call Upon per Year</t>
+  </si>
+  <si>
+    <t>DRC Average DR Hours per DR Event</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>Hours of Shift DR Average Utility May Call Upon per Year and Average DR Hours per Day on Days When DR is Called Upon</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>undated</t>
+  </si>
+  <si>
+    <t>Demand Response and Time-Variable Pricing Programs: Western States</t>
+  </si>
+  <si>
+    <t>https://www.energy.gov/eere/femp/demand-response-and-time-variable-pricing-programs-western-states</t>
+  </si>
+  <si>
+    <t>Using "California Independent System Operator (CAISO) Proxy Demand Response and Reliability Demand Response program" (under "California" section)</t>
+  </si>
+  <si>
+    <t>2019 Capacity and 2030 Projection</t>
+  </si>
+  <si>
+    <t>Brattle Group</t>
+  </si>
+  <si>
+    <t>The National Potential for Load Flexibility</t>
+  </si>
+  <si>
+    <t>https://brattlefiles.blob.core.windows.net/files/16639_national_potential_for_load_flexibility_-_final.pdf</t>
+  </si>
+  <si>
+    <t>Slide 18</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Demand response is defined as the potential to reduce or shift electricity usage during peak</t>
+  </si>
+  <si>
+    <t>periods in response to time-based rates or other financial incentives.</t>
+  </si>
+  <si>
+    <t>Although the Electricity Industry Law defines the Demand Control activity, it is not regulated and therefore does not exist as an operational tool for the National Energy Control Center Cenace.</t>
+  </si>
+  <si>
+    <t>It is estimated that a maximum of 50% of industrial and transport sector demand is adaptable to economic and regulatory signals.</t>
+  </si>
+  <si>
+    <t>We also require input data on the total number of hours of DR the average utility may call upon per year</t>
+  </si>
+  <si>
+    <t>and the typical length of each DR event in hours.  These are used to apportion the DR capacity to different</t>
+  </si>
+  <si>
+    <t>days and hours correctly in the model.</t>
+  </si>
+  <si>
+    <t>Brattle Capacity Projections (MW)</t>
+  </si>
+  <si>
+    <t>Peak Demand - EPS Output</t>
+  </si>
+  <si>
+    <t>Time (Year)</t>
+  </si>
+  <si>
+    <t>Peak Power Demand after Storage and DR[summer] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>DR Hours per Year and per Event</t>
+  </si>
+  <si>
+    <t>CAISO's Proxy Demand Response and Reliability Demand Response programs specifies:</t>
+  </si>
+  <si>
+    <t>Max of 48 hours of DR per 6-month period (96 per year)</t>
+  </si>
+  <si>
+    <t>Participants must be able to maintain demand reduction for at least 4 hours per DR event</t>
+  </si>
+  <si>
+    <t>Hours of Shift DR per Year</t>
+  </si>
+  <si>
+    <t>Hours of DR per Event</t>
+  </si>
+  <si>
+    <t>Mexico-U.S. Ratios</t>
+  </si>
   <si>
     <t>Year</t>
   </si>
   <si>
+    <t>GDP</t>
+  </si>
+  <si>
+    <t>implementation curve</t>
+  </si>
+  <si>
+    <t>For source information and calculations,</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>see "Mexico US Scaling Factors.xlsx"</t>
+  </si>
+  <si>
+    <t>in the InputData folder.</t>
+  </si>
+  <si>
+    <t>DR Capacity (MW)</t>
+  </si>
+  <si>
     <t>Potential Additional DR Capacity (MW)</t>
   </si>
   <si>
-    <t>DR Capacity (MW)</t>
-  </si>
-  <si>
-    <t>DRC BAU Demand Response Capacity</t>
-  </si>
-  <si>
-    <t>DRC Potential Additional Demand Response Capacity</t>
-  </si>
-  <si>
-    <t>Demand response is defined as the potential to reduce or shift electricity usage during peak</t>
-  </si>
-  <si>
-    <t>periods in response to time-based rates or other financial incentives.</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>https://brattlefiles.blob.core.windows.net/files/16639_national_potential_for_load_flexibility_-_final.pdf</t>
-  </si>
-  <si>
-    <t>Brattle Group</t>
-  </si>
-  <si>
-    <t>The National Potential for Load Flexibility</t>
-  </si>
-  <si>
-    <t>Slide 18</t>
-  </si>
-  <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>Brattle Capacity Projections (MW)</t>
-  </si>
-  <si>
-    <t>2019 Capacity and 2030 Projection</t>
-  </si>
-  <si>
-    <t>Time (Year)</t>
-  </si>
-  <si>
-    <t>Peak Demand - EPS Output</t>
-  </si>
-  <si>
-    <t>To estimate BAU DR Capacity, we scale Brattle's 2019 estimate of demand response potential by</t>
-  </si>
-  <si>
-    <t>the growth in peak demand (EPS model output).</t>
-  </si>
-  <si>
-    <t>We use a Brattle analysis to estimate the potential in 2030, and scale the potential between 2019 and 2030 linearly.</t>
-  </si>
-  <si>
-    <t>We then scale the potential from 2030 to 2050 by the growth in peak demand (EPS model output).</t>
-  </si>
-  <si>
-    <t>Peak Power Demand after Storage and DR[summer] : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Mexico-U.S. Ratios</t>
-  </si>
-  <si>
-    <t>GDP</t>
-  </si>
-  <si>
-    <t>For source information and calculations,</t>
-  </si>
-  <si>
-    <t>see "Mexico US Scaling Factors.xlsx"</t>
-  </si>
-  <si>
-    <t>in the InputData folder.</t>
-  </si>
-  <si>
-    <t>Mexico Values are scaled with GDP</t>
-  </si>
-  <si>
-    <t>implementation curve</t>
-  </si>
-  <si>
-    <t>factor</t>
+    <t>Unit: hours</t>
+  </si>
+  <si>
+    <t>Hours per Event</t>
+  </si>
+  <si>
+    <t>DR Hours per DR Event</t>
   </si>
 </sst>
 </file>
@@ -134,7 +194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +224,18 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Consolas"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -201,16 +273,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -220,7 +285,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -228,6 +300,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF1F497D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -239,10 +316,23 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Data and Calculations"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -280,9 +370,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -315,26 +405,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -367,26 +440,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -560,175 +616,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="2" max="2" width="107.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="B7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10" t="s">
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" s="2">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="2">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="6"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="6"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="5"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B31" s="6"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B11" r:id="rId1" xr:uid="{ED657289-6392-4C66-9FE3-F246C2AB4CF4}"/>
+    <hyperlink ref="B18" r:id="rId2" xr:uid="{67680684-34F5-4783-8B64-A0DEA4A4A5C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AH7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AH22"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-    </row>
-    <row r="2" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+    <row r="1" spans="1:34">
+      <c r="A1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:34">
+      <c r="A2">
         <v>2019</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2">
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>59000</v>
       </c>
@@ -736,14 +787,14 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="5" spans="1:34" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" s="6" customFormat="1">
+      <c r="A5" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>2019</v>
@@ -842,9 +893,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>752136</v>
@@ -906,43 +957,85 @@
       <c r="U7">
         <v>836502</v>
       </c>
-      <c r="V7" s="12">
+      <c r="V7" s="7">
         <v>841698</v>
       </c>
-      <c r="W7" s="12">
+      <c r="W7" s="7">
         <v>847887</v>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="7">
         <v>853549</v>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="7">
         <v>859603</v>
       </c>
-      <c r="Z7" s="12">
+      <c r="Z7" s="7">
         <v>866464</v>
       </c>
-      <c r="AA7" s="12">
+      <c r="AA7" s="7">
         <v>873306</v>
       </c>
-      <c r="AB7" s="12">
+      <c r="AB7" s="7">
         <v>881021</v>
       </c>
-      <c r="AC7" s="12">
+      <c r="AC7" s="7">
         <v>888875</v>
       </c>
-      <c r="AD7" s="12">
+      <c r="AD7" s="7">
         <v>896015</v>
       </c>
-      <c r="AE7" s="12">
+      <c r="AE7" s="7">
         <v>903925</v>
       </c>
-      <c r="AF7" s="12">
+      <c r="AF7" s="7">
         <v>912866</v>
       </c>
-      <c r="AG7" s="12">
+      <c r="AG7" s="7">
         <v>922440</v>
       </c>
-      <c r="AH7" s="12"/>
+      <c r="AH7" s="7"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -953,27 +1046,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2C662D-3E4B-D847-BD9D-5DB361B9A6C7}">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="13" width="9.140625"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>0</v>
+    <row r="1" spans="1:39">
+      <c r="A1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="C1">
         <v>2014</v>
@@ -1087,413 +1181,413 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A2" s="9"/>
-      <c r="B2" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="14">
+    <row r="2" spans="1:39">
+      <c r="A2" s="5"/>
+      <c r="B2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="9">
         <v>9.8636644841800333E-2</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.1003252824664638</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.10104496285900474</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>0.10152702997943744</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>0.10197979351839384</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="9">
         <v>0.10245639964773269</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="9">
         <v>0.10296756277334541</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="9">
         <v>0.10340803251068771</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="9">
         <v>0.10388755191988928</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="9">
         <v>0.10440602714772437</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="9">
         <v>0.10496009002297045</v>
       </c>
-      <c r="N2" s="14">
+      <c r="N2" s="9">
         <v>0.10556555417442678</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="9">
         <v>0.10600870488733041</v>
       </c>
-      <c r="P2" s="14">
+      <c r="P2" s="9">
         <v>0.10652912605952648</v>
       </c>
-      <c r="Q2" s="14">
+      <c r="Q2" s="9">
         <v>0.10713820378721554</v>
       </c>
-      <c r="R2" s="14">
+      <c r="R2" s="9">
         <v>0.1078432446493542</v>
       </c>
-      <c r="S2" s="14">
+      <c r="S2" s="9">
         <v>0.10864823793881466</v>
       </c>
-      <c r="T2" s="14">
+      <c r="T2" s="9">
         <v>0.10949499278959707</v>
       </c>
-      <c r="U2" s="14">
+      <c r="U2" s="9">
         <v>0.11043742468059306</v>
       </c>
-      <c r="V2" s="14">
+      <c r="V2" s="9">
         <v>0.11146883731544265</v>
       </c>
-      <c r="W2" s="14">
+      <c r="W2" s="9">
         <v>0.11257986730772145</v>
       </c>
-      <c r="X2" s="14">
+      <c r="X2" s="9">
         <v>0.11375854360098116</v>
       </c>
-      <c r="Y2" s="14">
+      <c r="Y2" s="9">
         <v>0.11500700295303776</v>
       </c>
-      <c r="Z2" s="14">
+      <c r="Z2" s="9">
         <v>0.11629345638152376</v>
       </c>
-      <c r="AA2" s="14">
+      <c r="AA2" s="9">
         <v>0.11760210049057489</v>
       </c>
-      <c r="AB2" s="14">
+      <c r="AB2" s="9">
         <v>0.11891740974492833</v>
       </c>
-      <c r="AC2" s="14">
+      <c r="AC2" s="9">
         <v>0.12022482270847104</v>
       </c>
-      <c r="AD2" s="14">
+      <c r="AD2" s="9">
         <v>0.1217335942417123</v>
       </c>
-      <c r="AE2" s="14">
+      <c r="AE2" s="9">
         <v>0.12321472992477742</v>
       </c>
-      <c r="AF2" s="14">
+      <c r="AF2" s="9">
         <v>0.12465772297340184</v>
       </c>
-      <c r="AG2" s="14">
+      <c r="AG2" s="9">
         <v>0.12605355536241392</v>
       </c>
-      <c r="AH2" s="14">
+      <c r="AH2" s="9">
         <v>0.12739430164149732</v>
       </c>
-      <c r="AI2" s="14">
+      <c r="AI2" s="9">
         <v>0.12879656057806463</v>
       </c>
-      <c r="AJ2" s="14">
+      <c r="AJ2" s="9">
         <v>0.13011576903115954</v>
       </c>
-      <c r="AK2" s="14">
+      <c r="AK2" s="9">
         <v>0.13135142612657708</v>
       </c>
-      <c r="AL2" s="14">
+      <c r="AL2" s="9">
         <v>0.13250370221109664</v>
       </c>
-      <c r="AM2" s="14">
+      <c r="AM2" s="9">
         <v>0.13357320132464462</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39">
       <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="14">
-        <v>0</v>
-      </c>
-      <c r="D3" s="14">
-        <v>0</v>
-      </c>
-      <c r="E3" s="14">
-        <v>0</v>
-      </c>
-      <c r="F3" s="14">
-        <v>0</v>
-      </c>
-      <c r="G3" s="14">
-        <v>0</v>
-      </c>
-      <c r="H3" s="14">
-        <v>0</v>
-      </c>
-      <c r="I3" s="14">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14">
-        <v>0</v>
-      </c>
-      <c r="K3" s="14">
-        <v>0</v>
-      </c>
-      <c r="L3" s="14">
-        <v>0</v>
-      </c>
-      <c r="M3" s="14">
-        <v>0</v>
-      </c>
-      <c r="N3" s="14">
+        <v>37</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
         <f t="shared" ref="N3:W3" si="0">(($X3-$M3)/($X1-$M1))*(N1-$M1)+$M3</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="9">
         <f t="shared" si="0"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="9">
         <f t="shared" si="0"/>
         <v>0.27272727272727271</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="9">
         <f t="shared" si="0"/>
         <v>0.36363636363636365</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="9">
         <f t="shared" si="0"/>
         <v>0.45454545454545459</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="9">
         <f t="shared" si="0"/>
         <v>0.54545454545454541</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="9">
         <f t="shared" si="0"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U3" s="14">
+      <c r="U3" s="9">
         <f t="shared" si="0"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="V3" s="14">
+      <c r="V3" s="9">
         <f t="shared" si="0"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="W3" s="14">
+      <c r="W3" s="9">
         <f t="shared" si="0"/>
         <v>0.90909090909090917</v>
       </c>
-      <c r="X3" s="14">
+      <c r="X3" s="9">
         <v>1</v>
       </c>
-      <c r="Y3" s="14">
+      <c r="Y3" s="9">
         <v>1</v>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="9">
         <v>1</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="9">
         <v>1</v>
       </c>
-      <c r="AB3" s="14">
+      <c r="AB3" s="9">
         <v>1</v>
       </c>
-      <c r="AC3" s="14">
+      <c r="AC3" s="9">
         <v>1</v>
       </c>
-      <c r="AD3" s="14">
+      <c r="AD3" s="9">
         <v>1</v>
       </c>
-      <c r="AE3" s="14">
+      <c r="AE3" s="9">
         <v>1</v>
       </c>
-      <c r="AF3" s="14">
+      <c r="AF3" s="9">
         <v>1</v>
       </c>
-      <c r="AG3" s="14">
+      <c r="AG3" s="9">
         <v>1</v>
       </c>
-      <c r="AH3" s="14">
+      <c r="AH3" s="9">
         <v>1</v>
       </c>
-      <c r="AI3" s="14">
+      <c r="AI3" s="9">
         <v>1</v>
       </c>
-      <c r="AJ3" s="14">
+      <c r="AJ3" s="9">
         <v>1</v>
       </c>
-      <c r="AK3" s="14">
+      <c r="AK3" s="9">
         <v>1</v>
       </c>
-      <c r="AL3" s="14">
+      <c r="AL3" s="9">
         <v>1</v>
       </c>
-      <c r="AM3" s="14">
+      <c r="AM3" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
-        <v>24</v>
+    <row r="4" spans="1:39">
+      <c r="A4" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="14">
+        <v>39</v>
+      </c>
+      <c r="C4" s="9">
         <f t="shared" ref="C4:AM4" si="1">C2*C3</f>
         <v>0</v>
       </c>
-      <c r="D4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="14">
+      <c r="D4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
         <f t="shared" si="1"/>
         <v>9.5968685613115265E-3</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="9">
         <f t="shared" si="1"/>
         <v>1.9274309979514622E-2</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="9">
         <f t="shared" si="1"/>
         <v>2.9053398016234494E-2</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="9">
         <f t="shared" si="1"/>
         <v>3.8959346831714745E-2</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="9">
         <f t="shared" si="1"/>
         <v>4.9019656658797366E-2</v>
       </c>
-      <c r="S4" s="14">
+      <c r="S4" s="9">
         <f t="shared" si="1"/>
         <v>5.9262675239353448E-2</v>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="9">
         <f t="shared" si="1"/>
         <v>6.9678631775198133E-2</v>
       </c>
-      <c r="U4" s="14">
+      <c r="U4" s="9">
         <f t="shared" si="1"/>
         <v>8.0318127040431314E-2</v>
       </c>
-      <c r="V4" s="14">
+      <c r="V4" s="9">
         <f t="shared" si="1"/>
         <v>9.1201775985362166E-2</v>
       </c>
-      <c r="W4" s="14">
+      <c r="W4" s="9">
         <f t="shared" si="1"/>
         <v>0.10234533391611042</v>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="9">
         <f t="shared" si="1"/>
         <v>0.11375854360098116</v>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="9">
         <f t="shared" si="1"/>
         <v>0.11500700295303776</v>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="9">
         <f t="shared" si="1"/>
         <v>0.11629345638152376</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="9">
         <f t="shared" si="1"/>
         <v>0.11760210049057489</v>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4" s="9">
         <f t="shared" si="1"/>
         <v>0.11891740974492833</v>
       </c>
-      <c r="AC4" s="14">
+      <c r="AC4" s="9">
         <f t="shared" si="1"/>
         <v>0.12022482270847104</v>
       </c>
-      <c r="AD4" s="14">
+      <c r="AD4" s="9">
         <f t="shared" si="1"/>
         <v>0.1217335942417123</v>
       </c>
-      <c r="AE4" s="14">
+      <c r="AE4" s="9">
         <f t="shared" si="1"/>
         <v>0.12321472992477742</v>
       </c>
-      <c r="AF4" s="14">
+      <c r="AF4" s="9">
         <f t="shared" si="1"/>
         <v>0.12465772297340184</v>
       </c>
-      <c r="AG4" s="14">
+      <c r="AG4" s="9">
         <f t="shared" si="1"/>
         <v>0.12605355536241392</v>
       </c>
-      <c r="AH4" s="14">
+      <c r="AH4" s="9">
         <f t="shared" si="1"/>
         <v>0.12739430164149732</v>
       </c>
-      <c r="AI4" s="14">
+      <c r="AI4" s="9">
         <f t="shared" si="1"/>
         <v>0.12879656057806463</v>
       </c>
-      <c r="AJ4" s="14">
+      <c r="AJ4" s="9">
         <f t="shared" si="1"/>
         <v>0.13011576903115954</v>
       </c>
-      <c r="AK4" s="14">
+      <c r="AK4" s="9">
         <f t="shared" si="1"/>
         <v>0.13135142612657708</v>
       </c>
-      <c r="AL4" s="14">
+      <c r="AL4" s="9">
         <f t="shared" si="1"/>
         <v>0.13250370221109664</v>
       </c>
-      <c r="AM4" s="14">
+      <c r="AM4" s="9">
         <f t="shared" si="1"/>
         <v>0.13357320132464462</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>26</v>
+    <row r="5" spans="1:39">
+      <c r="A5" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39">
+      <c r="A6" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1507,15 +1601,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AH16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B1">
         <v>2018</v>
@@ -1617,142 +1711,145 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34">
       <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C2" s="8">
-        <f>Calculations!A3*'Scaling Factors'!H4</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
-        <f>(Calculations!$A3)*(Calculations!C7/Calculations!$B$7)*'Scaling Factors'!I4</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="8">
-        <f>(Calculations!$A3)*(Calculations!D7/Calculations!$B$7)*'Scaling Factors'!J4</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="8">
-        <f>(Calculations!$A3)*(Calculations!E7/Calculations!$B$7)*'Scaling Factors'!K4</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="8">
-        <f>(Calculations!$A3)*(Calculations!F7/Calculations!$B$7)*'Scaling Factors'!L4</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="8">
-        <f>(Calculations!$A3)*(Calculations!G7/Calculations!$B$7)*'Scaling Factors'!M4</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="8">
-        <f>(Calculations!$A3)*(Calculations!H7/Calculations!$B$7)*'Scaling Factors'!N4</f>
+      <c r="C2" s="13">
+        <f>'Data and Calculations'!A3*'Scaling Factors'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!C7/'Data and Calculations'!$B$7)*'Scaling Factors'!I4</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!D7/'Data and Calculations'!$B$7)*'Scaling Factors'!J4</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!E7/'Data and Calculations'!$B$7)*'Scaling Factors'!K4</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!F7/'Data and Calculations'!$B$7)*'Scaling Factors'!L4</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!G7/'Data and Calculations'!$B$7)*'Scaling Factors'!M4</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!H7/'Data and Calculations'!$B$7)*'Scaling Factors'!N4</f>
         <v>581.54169694968789</v>
       </c>
-      <c r="J2" s="8">
-        <f>(Calculations!$A3)*(Calculations!I7/Calculations!$B$7)*'Scaling Factors'!O4</f>
+      <c r="J2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!I7/'Data and Calculations'!$B$7)*'Scaling Factors'!O4</f>
         <v>1174.3825415769413</v>
       </c>
-      <c r="K2" s="8">
-        <f>(Calculations!$A3)*(Calculations!J7/Calculations!$B$7)*'Scaling Factors'!P4</f>
+      <c r="K2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!J7/'Data and Calculations'!$B$7)*'Scaling Factors'!P4</f>
         <v>1776.8765906596982</v>
       </c>
-      <c r="L2" s="8">
-        <f>(Calculations!$A3)*(Calculations!K7/Calculations!$B$7)*'Scaling Factors'!Q4</f>
+      <c r="L2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!K7/'Data and Calculations'!$B$7)*'Scaling Factors'!Q4</f>
         <v>2397.4020612337731</v>
       </c>
-      <c r="M2" s="8">
-        <f>(Calculations!$A3)*(Calculations!L7/Calculations!$B$7)*'Scaling Factors'!R4</f>
+      <c r="M2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!L7/'Data and Calculations'!$B$7)*'Scaling Factors'!R4</f>
         <v>3046.7392626145902</v>
       </c>
-      <c r="N2" s="8">
-        <f>(Calculations!$A3)*(Calculations!M7/Calculations!$B$7)*'Scaling Factors'!S4</f>
+      <c r="N2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!M7/'Data and Calculations'!$B$7)*'Scaling Factors'!S4</f>
         <v>3702.6469885786787</v>
       </c>
-      <c r="O2" s="8">
-        <f>(Calculations!$A3)*(Calculations!N7/Calculations!$B$7)*'Scaling Factors'!T4</f>
+      <c r="O2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!N7/'Data and Calculations'!$B$7)*'Scaling Factors'!T4</f>
         <v>4377.8313682399566</v>
       </c>
-      <c r="P2" s="8">
-        <f>(Calculations!$A3)*(Calculations!O7/Calculations!$B$7)*'Scaling Factors'!U4</f>
+      <c r="P2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!O7/'Data and Calculations'!$B$7)*'Scaling Factors'!U4</f>
         <v>5078.9730442680011</v>
       </c>
-      <c r="Q2" s="8">
-        <f>(Calculations!$A3)*(Calculations!P7/Calculations!$B$7)*'Scaling Factors'!V4</f>
+      <c r="Q2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!P7/'Data and Calculations'!$B$7)*'Scaling Factors'!V4</f>
         <v>5797.5060990308293</v>
       </c>
-      <c r="R2" s="8">
-        <f>(Calculations!$A3)*(Calculations!Q7/Calculations!$B$7)*'Scaling Factors'!W4</f>
+      <c r="R2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!Q7/'Data and Calculations'!$B$7)*'Scaling Factors'!W4</f>
         <v>6540.2880645383366</v>
       </c>
-      <c r="S2" s="8">
-        <f>(Calculations!$A3)*(Calculations!R7/Calculations!$B$7)*'Scaling Factors'!X4</f>
+      <c r="S2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!R7/'Data and Calculations'!$B$7)*'Scaling Factors'!X4</f>
         <v>7315.6313254963943</v>
       </c>
-      <c r="T2" s="8">
-        <f>(Calculations!$A3)*(Calculations!S7/Calculations!$B$7)*'Scaling Factors'!Y4</f>
+      <c r="T2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!S7/'Data and Calculations'!$B$7)*'Scaling Factors'!Y4</f>
         <v>7440.5382232711263</v>
       </c>
-      <c r="U2" s="8">
-        <f>(Calculations!$A3)*(Calculations!T7/Calculations!$B$7)*'Scaling Factors'!Z4</f>
+      <c r="U2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!T7/'Data and Calculations'!$B$7)*'Scaling Factors'!Z4</f>
         <v>7580.7276214698877</v>
       </c>
-      <c r="V2" s="8">
-        <f>(Calculations!$A3)*(Calculations!U7/Calculations!$B$7)*'Scaling Factors'!AA4</f>
+      <c r="V2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!U7/'Data and Calculations'!$B$7)*'Scaling Factors'!AA4</f>
         <v>7716.8080554706139</v>
       </c>
-      <c r="W2" s="8">
-        <f>(Calculations!$A3)*(Calculations!V7/Calculations!$B$7)*'Scaling Factors'!AB4</f>
+      <c r="W2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!V7/'Data and Calculations'!$B$7)*'Scaling Factors'!AB4</f>
         <v>7851.5856319890481</v>
       </c>
-      <c r="X2" s="8">
-        <f>(Calculations!$A3)*(Calculations!W7/Calculations!$B$7)*'Scaling Factors'!AC4</f>
+      <c r="X2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!W7/'Data and Calculations'!$B$7)*'Scaling Factors'!AC4</f>
         <v>7996.275661392654</v>
       </c>
-      <c r="Y2" s="8">
-        <f>(Calculations!$A3)*(Calculations!X7/Calculations!$B$7)*'Scaling Factors'!AD4</f>
+      <c r="Y2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!X7/'Data and Calculations'!$B$7)*'Scaling Factors'!AD4</f>
         <v>8150.6930531894996</v>
       </c>
-      <c r="Z2" s="8">
-        <f>(Calculations!$A3)*(Calculations!Y7/Calculations!$B$7)*'Scaling Factors'!AE4</f>
+      <c r="Z2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!Y7/'Data and Calculations'!$B$7)*'Scaling Factors'!AE4</f>
         <v>8308.3768597224152</v>
       </c>
-      <c r="AA2" s="8">
-        <f>(Calculations!$A3)*(Calculations!Z7/Calculations!$B$7)*'Scaling Factors'!AF4</f>
+      <c r="AA2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!Z7/'Data and Calculations'!$B$7)*'Scaling Factors'!AF4</f>
         <v>8472.7686580978898</v>
       </c>
-      <c r="AB2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AA7/Calculations!$B$7)*'Scaling Factors'!AG4</f>
+      <c r="AB2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AA7/'Data and Calculations'!$B$7)*'Scaling Factors'!AG4</f>
         <v>8635.2950090679969</v>
       </c>
-      <c r="AC2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AB7/Calculations!$B$7)*'Scaling Factors'!AH4</f>
+      <c r="AC2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AB7/'Data and Calculations'!$B$7)*'Scaling Factors'!AH4</f>
         <v>8804.2405184210347</v>
       </c>
-      <c r="AD2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AC7/Calculations!$B$7)*'Scaling Factors'!AI4</f>
+      <c r="AD2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AC7/'Data and Calculations'!$B$7)*'Scaling Factors'!AI4</f>
         <v>8980.5015638738259</v>
       </c>
-      <c r="AE2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AD7/Calculations!$B$7)*'Scaling Factors'!AJ4</f>
+      <c r="AE2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AD7/'Data and Calculations'!$B$7)*'Scaling Factors'!AJ4</f>
         <v>9145.3609008461372</v>
       </c>
-      <c r="AF2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AE7/Calculations!$B$7)*'Scaling Factors'!AK4</f>
+      <c r="AF2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AE7/'Data and Calculations'!$B$7)*'Scaling Factors'!AK4</f>
         <v>9313.7124586863356</v>
       </c>
-      <c r="AG2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AF7/Calculations!$B$7)*'Scaling Factors'!AL4</f>
+      <c r="AG2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AF7/'Data and Calculations'!$B$7)*'Scaling Factors'!AL4</f>
         <v>9488.3496505092971</v>
       </c>
-      <c r="AH2" s="8">
-        <f>(Calculations!$A3)*(Calculations!AG7/Calculations!$B$7)*'Scaling Factors'!AM4</f>
+      <c r="AH2" s="4">
+        <f>('Data and Calculations'!$A3)*('Data and Calculations'!AG7/'Data and Calculations'!$B$7)*'Scaling Factors'!AM4</f>
         <v>9665.2501222709798</v>
       </c>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="E16" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1765,14 +1862,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B1">
         <v>2018</v>
@@ -1874,144 +1971,345 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34">
       <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8">
+        <v>43</v>
+      </c>
+      <c r="B2" s="4">
         <f>C2*'Scaling Factors'!G2</f>
-        <v>616.46046636211531</v>
-      </c>
-      <c r="C2" s="8">
-        <f>Calculations!A3*'Scaling Factors'!H2-'DRC-BDRC'!C2</f>
-        <v>6044.9275792162289</v>
-      </c>
-      <c r="D2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!D1)*'Scaling Factors'!I2-'DRC-BDRC'!D2</f>
+        <v>410.56326324847817</v>
+      </c>
+      <c r="C2" s="15">
+        <f>'Data and Calculations'!A3*'Scaling Factors'!H2-'DRC-BDRC'!C1</f>
+        <v>4025.9275792162289</v>
+      </c>
+      <c r="D2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!D1)*'Scaling Factors'!I2-'DRC-BDRC'!D2</f>
         <v>7376.221769581437</v>
       </c>
-      <c r="E2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!E1)*'Scaling Factors'!J2-'DRC-BDRC'!E2</f>
+      <c r="E2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!E1)*'Scaling Factors'!J2-'DRC-BDRC'!E2</f>
         <v>8714.4769215828164</v>
       </c>
-      <c r="F2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!F1)*'Scaling Factors'!K2-'DRC-BDRC'!F2</f>
+      <c r="F2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!F1)*'Scaling Factors'!K2-'DRC-BDRC'!F2</f>
         <v>10067.648213327733</v>
       </c>
-      <c r="G2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!G1)*'Scaling Factors'!L2-'DRC-BDRC'!G2</f>
+      <c r="G2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!G1)*'Scaling Factors'!L2-'DRC-BDRC'!G2</f>
         <v>11437.205701182782</v>
       </c>
-      <c r="H2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!H1)*'Scaling Factors'!M2-'DRC-BDRC'!H2</f>
+      <c r="H2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!H1)*'Scaling Factors'!M2-'DRC-BDRC'!H2</f>
         <v>12824.214635534057</v>
       </c>
-      <c r="I2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!I1)*'Scaling Factors'!N2-'DRC-BDRC'!I2</f>
+      <c r="I2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!I1)*'Scaling Factors'!N2-'DRC-BDRC'!I2</f>
         <v>13650.614379475484</v>
       </c>
-      <c r="J2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!J1)*'Scaling Factors'!O2-'DRC-BDRC'!J2</f>
+      <c r="J2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!J1)*'Scaling Factors'!O2-'DRC-BDRC'!J2</f>
         <v>14457.08285180956</v>
       </c>
-      <c r="K2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!K1)*'Scaling Factors'!P2-'DRC-BDRC'!K2</f>
+      <c r="K2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!K1)*'Scaling Factors'!P2-'DRC-BDRC'!K2</f>
         <v>15277.468044870058</v>
       </c>
-      <c r="L2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!L1)*'Scaling Factors'!Q2-'DRC-BDRC'!L2</f>
+      <c r="L2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!L1)*'Scaling Factors'!Q2-'DRC-BDRC'!L2</f>
         <v>16108.287683830804</v>
       </c>
-      <c r="M2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!M1)*'Scaling Factors'!R2-'DRC-BDRC'!M2</f>
+      <c r="M2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!M1)*'Scaling Factors'!R2-'DRC-BDRC'!M2</f>
         <v>16943.476722843014</v>
       </c>
-      <c r="N2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!N1)*'Scaling Factors'!S2-'DRC-BDRC'!N2</f>
+      <c r="N2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!N1)*'Scaling Factors'!S2-'DRC-BDRC'!N2</f>
         <v>17809.704123306623</v>
       </c>
-      <c r="O2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!O1)*'Scaling Factors'!T2-'DRC-BDRC'!O2</f>
+      <c r="O2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!O1)*'Scaling Factors'!T2-'DRC-BDRC'!O2</f>
         <v>18685.795749350589</v>
       </c>
-      <c r="P2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!P1)*'Scaling Factors'!U2-'DRC-BDRC'!P2</f>
+      <c r="P2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!P1)*'Scaling Factors'!U2-'DRC-BDRC'!P2</f>
         <v>19578.691957144751</v>
       </c>
-      <c r="Q2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!Q1)*'Scaling Factors'!V2-'DRC-BDRC'!Q2</f>
+      <c r="Q2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!Q1)*'Scaling Factors'!V2-'DRC-BDRC'!Q2</f>
         <v>20499.005976748897</v>
       </c>
-      <c r="R2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!R1)*'Scaling Factors'!W2-'DRC-BDRC'!R2</f>
+      <c r="R2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!R1)*'Scaling Factors'!W2-'DRC-BDRC'!R2</f>
         <v>21440.926228126515</v>
       </c>
-      <c r="S2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!S1)*'Scaling Factors'!X2-'DRC-BDRC'!S2</f>
+      <c r="S2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!S1)*'Scaling Factors'!X2-'DRC-BDRC'!S2</f>
         <v>22396.031925923733</v>
       </c>
-      <c r="T2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!T1)*'Scaling Factors'!Y2-'DRC-BDRC'!T2</f>
+      <c r="T2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!T1)*'Scaling Factors'!Y2-'DRC-BDRC'!T2</f>
         <v>24050.470221688134</v>
       </c>
-      <c r="U2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!U1)*'Scaling Factors'!Z2-'DRC-BDRC'!U2</f>
+      <c r="U2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!U1)*'Scaling Factors'!Z2-'DRC-BDRC'!U2</f>
         <v>25732.061565637669</v>
       </c>
-      <c r="V2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!V1)*'Scaling Factors'!AA2-'DRC-BDRC'!V2</f>
+      <c r="V2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!V1)*'Scaling Factors'!AA2-'DRC-BDRC'!V2</f>
         <v>27456.911091255995</v>
       </c>
-      <c r="W2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!W1)*'Scaling Factors'!AB2-'DRC-BDRC'!W2</f>
+      <c r="W2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!W1)*'Scaling Factors'!AB2-'DRC-BDRC'!W2</f>
         <v>29218.214187589143</v>
       </c>
-      <c r="X2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!X1)*'Scaling Factors'!AC2-'DRC-BDRC'!X2</f>
+      <c r="X2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!X1)*'Scaling Factors'!AC2-'DRC-BDRC'!X2</f>
         <v>31000.285013500536</v>
       </c>
-      <c r="Y2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!Y1)*'Scaling Factors'!AD2-'DRC-BDRC'!Y2</f>
+      <c r="Y2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!Y1)*'Scaling Factors'!AD2-'DRC-BDRC'!Y2</f>
         <v>32873.528206267547</v>
       </c>
-      <c r="Z2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!Z1)*'Scaling Factors'!AE2-'DRC-BDRC'!Z2</f>
+      <c r="Z2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!Z1)*'Scaling Factors'!AE2-'DRC-BDRC'!Z2</f>
         <v>34771.973257613354</v>
       </c>
-      <c r="AA2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AA1)*'Scaling Factors'!AF2-'DRC-BDRC'!AA2</f>
+      <c r="AA2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AA1)*'Scaling Factors'!AF2-'DRC-BDRC'!AA2</f>
         <v>36687.32461908488</v>
       </c>
-      <c r="AB2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AB1)*'Scaling Factors'!AG2-'DRC-BDRC'!AB2</f>
+      <c r="AB2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AB1)*'Scaling Factors'!AG2-'DRC-BDRC'!AB2</f>
         <v>38623.328837713707</v>
       </c>
-      <c r="AC2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AC1)*'Scaling Factors'!AH2-'DRC-BDRC'!AC2</f>
+      <c r="AC2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AC1)*'Scaling Factors'!AH2-'DRC-BDRC'!AC2</f>
         <v>40566.842017734089</v>
       </c>
-      <c r="AD2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AD1)*'Scaling Factors'!AI2-'DRC-BDRC'!AD2</f>
+      <c r="AD2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AD1)*'Scaling Factors'!AI2-'DRC-BDRC'!AD2</f>
         <v>42561.540223821023</v>
       </c>
-      <c r="AE2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AE1)*'Scaling Factors'!AJ2-'DRC-BDRC'!AE2</f>
+      <c r="AE2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AE1)*'Scaling Factors'!AJ2-'DRC-BDRC'!AE2</f>
         <v>44568.794296471853</v>
       </c>
-      <c r="AF2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AF1)*'Scaling Factors'!AK2-'DRC-BDRC'!AF2</f>
+      <c r="AF2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AF1)*'Scaling Factors'!AK2-'DRC-BDRC'!AF2</f>
         <v>46570.348838802995</v>
       </c>
-      <c r="AG2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AG1)*'Scaling Factors'!AL2-'DRC-BDRC'!AG2</f>
+      <c r="AG2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AG1)*'Scaling Factors'!AL2-'DRC-BDRC'!AG2</f>
         <v>48560.317709061266</v>
       </c>
-      <c r="AH2" s="8">
-        <f>TREND(Calculations!$A$3:$B$3,Calculations!$A$2:$B$2,'DRC-PADRC'!AH1)*'Scaling Factors'!AM2-'DRC-BDRC'!AH2</f>
+      <c r="AH2" s="4">
+        <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AH1)*'Scaling Factors'!AM2-'DRC-BDRC'!AH2</f>
         <v>50539.834620237118</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C0DB4E4-8239-4A57-B4D1-910DA3EB7C22}">
+  <sheetPr>
+    <tabColor rgb="FF1F497D"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="16">
+        <f>ROUND('Data and Calculations'!A22,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD124F93-4C1F-4E6F-9FF6-BBDFC587A76D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC1EE97F-BEF3-4E27-B60F-7AF2FDABE2B4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EC3B175-1A50-44DD-A6FF-610DA475B8B5}"/>
 </file>
--- a/InputData/elec/DRC/Demand Response Capacity.xlsx
+++ b/InputData/elec/DRC/Demand Response Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28507"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/TARGET_eps-us-3.2.1/InputData/elec/DRC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\DRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{EAF18D30-C872-8641-B28C-E82493455792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85781D6E-DF9F-47DE-9867-BAA8E93E065C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0FABC8-E2D3-43E6-A08C-2D1399C1AE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="500" windowWidth="23960" windowHeight="12280" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="DRC-PADRC" sheetId="2" r:id="rId5"/>
     <sheet name="DRC-ADRHpDRE" sheetId="7" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -191,10 +188,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-  </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,12 +224,13 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
-      <charset val="1"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -266,7 +261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -277,22 +272,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -314,19 +310,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Data and Calculations"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -617,32 +600,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="107.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -650,98 +633,98 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>2019</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -759,19 +742,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -779,7 +762,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>59000</v>
       </c>
@@ -787,12 +770,12 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="5" spans="1:34" s="6" customFormat="1">
+    <row r="5" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -893,7 +876,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -995,44 +978,44 @@
       </c>
       <c r="AH7" s="7"/>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
@@ -1046,547 +1029,548 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2C662D-3E4B-D847-BD9D-5DB361B9A6C7}">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="13" width="9.140625"/>
-    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="9.140625" style="15"/>
+    <col min="14" max="14" width="16.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9" style="15" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.85546875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="15">
         <v>2014</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="15">
         <v>2015</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="15">
         <v>2016</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="15">
         <v>2017</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="15">
         <v>2018</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="15">
         <v>2019</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="15">
         <v>2020</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="15">
         <v>2021</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="15">
         <v>2022</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="15">
         <v>2023</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="15">
         <v>2024</v>
       </c>
-      <c r="N1">
+      <c r="N1" s="15">
         <v>2025</v>
       </c>
-      <c r="O1">
+      <c r="O1" s="15">
         <v>2026</v>
       </c>
-      <c r="P1">
+      <c r="P1" s="15">
         <v>2027</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" s="15">
         <v>2028</v>
       </c>
-      <c r="R1">
+      <c r="R1" s="15">
         <v>2029</v>
       </c>
-      <c r="S1">
+      <c r="S1" s="15">
         <v>2030</v>
       </c>
-      <c r="T1">
+      <c r="T1" s="15">
         <v>2031</v>
       </c>
-      <c r="U1">
+      <c r="U1" s="15">
         <v>2032</v>
       </c>
-      <c r="V1">
+      <c r="V1" s="15">
         <v>2033</v>
       </c>
-      <c r="W1">
+      <c r="W1" s="15">
         <v>2034</v>
       </c>
-      <c r="X1">
+      <c r="X1" s="15">
         <v>2035</v>
       </c>
-      <c r="Y1">
+      <c r="Y1" s="15">
         <v>2036</v>
       </c>
-      <c r="Z1">
+      <c r="Z1" s="15">
         <v>2037</v>
       </c>
-      <c r="AA1">
+      <c r="AA1" s="15">
         <v>2038</v>
       </c>
-      <c r="AB1">
+      <c r="AB1" s="15">
         <v>2039</v>
       </c>
-      <c r="AC1">
+      <c r="AC1" s="15">
         <v>2040</v>
       </c>
-      <c r="AD1">
+      <c r="AD1" s="15">
         <v>2041</v>
       </c>
-      <c r="AE1">
+      <c r="AE1" s="15">
         <v>2042</v>
       </c>
-      <c r="AF1">
+      <c r="AF1" s="15">
         <v>2043</v>
       </c>
-      <c r="AG1">
+      <c r="AG1" s="15">
         <v>2044</v>
       </c>
-      <c r="AH1">
+      <c r="AH1" s="15">
         <v>2045</v>
       </c>
-      <c r="AI1">
+      <c r="AI1" s="15">
         <v>2046</v>
       </c>
-      <c r="AJ1">
+      <c r="AJ1" s="15">
         <v>2047</v>
       </c>
-      <c r="AK1">
+      <c r="AK1" s="15">
         <v>2048</v>
       </c>
-      <c r="AL1">
+      <c r="AL1" s="15">
         <v>2049</v>
       </c>
-      <c r="AM1">
+      <c r="AM1" s="15">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:39">
-      <c r="A2" s="5"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="15">
         <v>9.8636644841800333E-2</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="15">
         <v>0.1003252824664638</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="15">
         <v>0.10104496285900474</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="15">
         <v>0.10152702997943744</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="15">
         <v>0.10197979351839384</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="15">
         <v>0.10245639964773269</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="15">
         <v>0.10296756277334541</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="15">
         <v>0.10340803251068771</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="15">
         <v>0.10388755191988928</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="15">
         <v>0.10440602714772437</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="15">
         <v>0.10496009002297045</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="15">
         <v>0.10556555417442678</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="15">
         <v>0.10600870488733041</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="15">
         <v>0.10652912605952648</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="15">
         <v>0.10713820378721554</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="15">
         <v>0.1078432446493542</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="15">
         <v>0.10864823793881466</v>
       </c>
-      <c r="T2" s="9">
+      <c r="T2" s="15">
         <v>0.10949499278959707</v>
       </c>
-      <c r="U2" s="9">
+      <c r="U2" s="15">
         <v>0.11043742468059306</v>
       </c>
-      <c r="V2" s="9">
+      <c r="V2" s="15">
         <v>0.11146883731544265</v>
       </c>
-      <c r="W2" s="9">
+      <c r="W2" s="15">
         <v>0.11257986730772145</v>
       </c>
-      <c r="X2" s="9">
+      <c r="X2" s="15">
         <v>0.11375854360098116</v>
       </c>
-      <c r="Y2" s="9">
+      <c r="Y2" s="15">
         <v>0.11500700295303776</v>
       </c>
-      <c r="Z2" s="9">
+      <c r="Z2" s="15">
         <v>0.11629345638152376</v>
       </c>
-      <c r="AA2" s="9">
+      <c r="AA2" s="15">
         <v>0.11760210049057489</v>
       </c>
-      <c r="AB2" s="9">
+      <c r="AB2" s="15">
         <v>0.11891740974492833</v>
       </c>
-      <c r="AC2" s="9">
+      <c r="AC2" s="15">
         <v>0.12022482270847104</v>
       </c>
-      <c r="AD2" s="9">
+      <c r="AD2" s="15">
         <v>0.1217335942417123</v>
       </c>
-      <c r="AE2" s="9">
+      <c r="AE2" s="15">
         <v>0.12321472992477742</v>
       </c>
-      <c r="AF2" s="9">
+      <c r="AF2" s="15">
         <v>0.12465772297340184</v>
       </c>
-      <c r="AG2" s="9">
+      <c r="AG2" s="15">
         <v>0.12605355536241392</v>
       </c>
-      <c r="AH2" s="9">
+      <c r="AH2" s="15">
         <v>0.12739430164149732</v>
       </c>
-      <c r="AI2" s="9">
+      <c r="AI2" s="15">
         <v>0.12879656057806463</v>
       </c>
-      <c r="AJ2" s="9">
+      <c r="AJ2" s="15">
         <v>0.13011576903115954</v>
       </c>
-      <c r="AK2" s="9">
+      <c r="AK2" s="15">
         <v>0.13135142612657708</v>
       </c>
-      <c r="AL2" s="9">
+      <c r="AL2" s="15">
         <v>0.13250370221109664</v>
       </c>
-      <c r="AM2" s="9">
+      <c r="AM2" s="15">
         <v>0.13357320132464462</v>
       </c>
     </row>
-    <row r="3" spans="1:39">
-      <c r="B3" t="s">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="9">
-        <v>0</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9">
-        <v>0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9">
+      <c r="C3" s="15">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0</v>
+      </c>
+      <c r="N3" s="15">
         <f t="shared" ref="N3:W3" si="0">(($X3-$M3)/($X1-$M1))*(N1-$M1)+$M3</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="15">
         <f t="shared" si="0"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="P3" s="9">
-        <f t="shared" si="0"/>
+      <c r="P3" s="15">
+        <f>(($X3-$M3)/($X1-$M1))*(P1-$M1)+$M3</f>
         <v>0.27272727272727271</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="Q3" s="15">
         <f t="shared" si="0"/>
         <v>0.36363636363636365</v>
       </c>
-      <c r="R3" s="9">
+      <c r="R3" s="15">
         <f t="shared" si="0"/>
         <v>0.45454545454545459</v>
       </c>
-      <c r="S3" s="9">
+      <c r="S3" s="15">
         <f t="shared" si="0"/>
         <v>0.54545454545454541</v>
       </c>
-      <c r="T3" s="9">
+      <c r="T3" s="15">
         <f t="shared" si="0"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="U3" s="9">
+      <c r="U3" s="15">
         <f t="shared" si="0"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="V3" s="9">
+      <c r="V3" s="15">
         <f t="shared" si="0"/>
         <v>0.81818181818181823</v>
       </c>
-      <c r="W3" s="9">
+      <c r="W3" s="15">
         <f t="shared" si="0"/>
         <v>0.90909090909090917</v>
       </c>
-      <c r="X3" s="9">
+      <c r="X3" s="15">
         <v>1</v>
       </c>
-      <c r="Y3" s="9">
+      <c r="Y3" s="15">
         <v>1</v>
       </c>
-      <c r="Z3" s="9">
+      <c r="Z3" s="15">
         <v>1</v>
       </c>
-      <c r="AA3" s="9">
+      <c r="AA3" s="15">
         <v>1</v>
       </c>
-      <c r="AB3" s="9">
+      <c r="AB3" s="15">
         <v>1</v>
       </c>
-      <c r="AC3" s="9">
+      <c r="AC3" s="15">
         <v>1</v>
       </c>
-      <c r="AD3" s="9">
+      <c r="AD3" s="15">
         <v>1</v>
       </c>
-      <c r="AE3" s="9">
+      <c r="AE3" s="15">
         <v>1</v>
       </c>
-      <c r="AF3" s="9">
+      <c r="AF3" s="15">
         <v>1</v>
       </c>
-      <c r="AG3" s="9">
+      <c r="AG3" s="15">
         <v>1</v>
       </c>
-      <c r="AH3" s="9">
+      <c r="AH3" s="15">
         <v>1</v>
       </c>
-      <c r="AI3" s="9">
+      <c r="AI3" s="15">
         <v>1</v>
       </c>
-      <c r="AJ3" s="9">
+      <c r="AJ3" s="15">
         <v>1</v>
       </c>
-      <c r="AK3" s="9">
+      <c r="AK3" s="15">
         <v>1</v>
       </c>
-      <c r="AL3" s="9">
+      <c r="AL3" s="15">
         <v>1</v>
       </c>
-      <c r="AM3" s="9">
+      <c r="AM3" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:39">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="15">
         <f t="shared" ref="C4:AM4" si="1">C2*C3</f>
         <v>0</v>
       </c>
-      <c r="D4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
+      <c r="D4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
         <f t="shared" si="1"/>
         <v>9.5968685613115265E-3</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="15">
         <f t="shared" si="1"/>
         <v>1.9274309979514622E-2</v>
       </c>
-      <c r="P4" s="9">
-        <f t="shared" si="1"/>
+      <c r="P4" s="15">
+        <f>P2*P3</f>
         <v>2.9053398016234494E-2</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="Q4" s="15">
         <f t="shared" si="1"/>
         <v>3.8959346831714745E-2</v>
       </c>
-      <c r="R4" s="9">
+      <c r="R4" s="15">
         <f t="shared" si="1"/>
         <v>4.9019656658797366E-2</v>
       </c>
-      <c r="S4" s="9">
+      <c r="S4" s="15">
         <f t="shared" si="1"/>
         <v>5.9262675239353448E-2</v>
       </c>
-      <c r="T4" s="9">
+      <c r="T4" s="15">
         <f t="shared" si="1"/>
         <v>6.9678631775198133E-2</v>
       </c>
-      <c r="U4" s="9">
+      <c r="U4" s="15">
         <f t="shared" si="1"/>
         <v>8.0318127040431314E-2</v>
       </c>
-      <c r="V4" s="9">
+      <c r="V4" s="15">
         <f t="shared" si="1"/>
         <v>9.1201775985362166E-2</v>
       </c>
-      <c r="W4" s="9">
+      <c r="W4" s="15">
         <f t="shared" si="1"/>
         <v>0.10234533391611042</v>
       </c>
-      <c r="X4" s="9">
+      <c r="X4" s="15">
         <f t="shared" si="1"/>
         <v>0.11375854360098116</v>
       </c>
-      <c r="Y4" s="9">
+      <c r="Y4" s="15">
         <f t="shared" si="1"/>
         <v>0.11500700295303776</v>
       </c>
-      <c r="Z4" s="9">
+      <c r="Z4" s="15">
         <f t="shared" si="1"/>
         <v>0.11629345638152376</v>
       </c>
-      <c r="AA4" s="9">
+      <c r="AA4" s="15">
         <f t="shared" si="1"/>
         <v>0.11760210049057489</v>
       </c>
-      <c r="AB4" s="9">
+      <c r="AB4" s="15">
         <f t="shared" si="1"/>
         <v>0.11891740974492833</v>
       </c>
-      <c r="AC4" s="9">
+      <c r="AC4" s="15">
         <f t="shared" si="1"/>
         <v>0.12022482270847104</v>
       </c>
-      <c r="AD4" s="9">
+      <c r="AD4" s="15">
         <f t="shared" si="1"/>
         <v>0.1217335942417123</v>
       </c>
-      <c r="AE4" s="9">
+      <c r="AE4" s="15">
         <f t="shared" si="1"/>
         <v>0.12321472992477742</v>
       </c>
-      <c r="AF4" s="9">
+      <c r="AF4" s="15">
         <f t="shared" si="1"/>
         <v>0.12465772297340184</v>
       </c>
-      <c r="AG4" s="9">
+      <c r="AG4" s="15">
         <f t="shared" si="1"/>
         <v>0.12605355536241392</v>
       </c>
-      <c r="AH4" s="9">
+      <c r="AH4" s="15">
         <f t="shared" si="1"/>
         <v>0.12739430164149732</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AI4" s="15">
         <f t="shared" si="1"/>
         <v>0.12879656057806463</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AJ4" s="15">
         <f t="shared" si="1"/>
         <v>0.13011576903115954</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AK4" s="15">
         <f t="shared" si="1"/>
         <v>0.13135142612657708</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AL4" s="15">
         <f t="shared" si="1"/>
         <v>0.13250370221109664</v>
       </c>
-      <c r="AM4" s="9">
+      <c r="AM4" s="15">
         <f t="shared" si="1"/>
         <v>0.13357320132464462</v>
       </c>
     </row>
-    <row r="5" spans="1:39">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:39">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1601,13 +1585,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AH16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:BD16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1710,8 +1694,68 @@
       <c r="AH1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
+      <c r="AI1">
+        <v>2051</v>
+      </c>
+      <c r="AJ1">
+        <v>2052</v>
+      </c>
+      <c r="AK1">
+        <v>2053</v>
+      </c>
+      <c r="AL1">
+        <v>2054</v>
+      </c>
+      <c r="AM1">
+        <v>2055</v>
+      </c>
+      <c r="AN1">
+        <v>2056</v>
+      </c>
+      <c r="AO1">
+        <v>2057</v>
+      </c>
+      <c r="AP1">
+        <v>2058</v>
+      </c>
+      <c r="AQ1">
+        <v>2059</v>
+      </c>
+      <c r="AR1">
+        <v>2060</v>
+      </c>
+      <c r="AS1">
+        <v>2061</v>
+      </c>
+      <c r="AT1">
+        <v>2062</v>
+      </c>
+      <c r="AU1">
+        <v>2063</v>
+      </c>
+      <c r="AV1">
+        <v>2064</v>
+      </c>
+      <c r="AW1">
+        <v>2065</v>
+      </c>
+      <c r="AX1">
+        <v>2066</v>
+      </c>
+      <c r="AY1">
+        <v>2067</v>
+      </c>
+      <c r="AZ1">
+        <v>2068</v>
+      </c>
+      <c r="BA1">
+        <v>2069</v>
+      </c>
+      <c r="BB1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1719,7 +1763,7 @@
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="10">
         <f>'Data and Calculations'!A3*'Scaling Factors'!H4</f>
         <v>0</v>
       </c>
@@ -1847,9 +1891,91 @@
         <f>('Data and Calculations'!$A3)*('Data and Calculations'!AG7/'Data and Calculations'!$B$7)*'Scaling Factors'!AM4</f>
         <v>9665.2501222709798</v>
       </c>
-    </row>
-    <row r="16" spans="1:34">
-      <c r="E16" s="12"/>
+      <c r="AI2" s="4">
+        <f>AH2</f>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" ref="AJ2:BB2" si="0">AI2</f>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="BA2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="BB2" s="4">
+        <f t="shared" si="0"/>
+        <v>9665.2501222709798</v>
+      </c>
+      <c r="BC2" s="4"/>
+      <c r="BD2" s="4"/>
+    </row>
+    <row r="16" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="E16" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1861,13 +1987,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:BB2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1970,16 +2096,76 @@
       <c r="AH1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
-      <c r="A2" s="17" t="s">
+      <c r="AI1">
+        <v>2051</v>
+      </c>
+      <c r="AJ1">
+        <v>2052</v>
+      </c>
+      <c r="AK1">
+        <v>2053</v>
+      </c>
+      <c r="AL1">
+        <v>2054</v>
+      </c>
+      <c r="AM1">
+        <v>2055</v>
+      </c>
+      <c r="AN1">
+        <v>2056</v>
+      </c>
+      <c r="AO1">
+        <v>2057</v>
+      </c>
+      <c r="AP1">
+        <v>2058</v>
+      </c>
+      <c r="AQ1">
+        <v>2059</v>
+      </c>
+      <c r="AR1">
+        <v>2060</v>
+      </c>
+      <c r="AS1">
+        <v>2061</v>
+      </c>
+      <c r="AT1">
+        <v>2062</v>
+      </c>
+      <c r="AU1">
+        <v>2063</v>
+      </c>
+      <c r="AV1">
+        <v>2064</v>
+      </c>
+      <c r="AW1">
+        <v>2065</v>
+      </c>
+      <c r="AX1">
+        <v>2066</v>
+      </c>
+      <c r="AY1">
+        <v>2067</v>
+      </c>
+      <c r="AZ1">
+        <v>2068</v>
+      </c>
+      <c r="BA1">
+        <v>2069</v>
+      </c>
+      <c r="BB1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="4">
         <f>C2*'Scaling Factors'!G2</f>
         <v>410.56326324847817</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="12">
         <f>'Data and Calculations'!A3*'Scaling Factors'!H2-'DRC-BDRC'!C1</f>
         <v>4025.9275792162289</v>
       </c>
@@ -2105,6 +2291,86 @@
       </c>
       <c r="AH2" s="4">
         <f>TREND('Data and Calculations'!$A$3:$B$3,'Data and Calculations'!$A$2:$B$2,'DRC-PADRC'!AH1)*'Scaling Factors'!AM2-'DRC-BDRC'!AH2</f>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AI2" s="4">
+        <f>AH2</f>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AJ2" s="4">
+        <f t="shared" ref="AJ2:BB2" si="0">AI2</f>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AK2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AL2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AM2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AN2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AO2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AP2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AR2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AS2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AT2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AU2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AV2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AW2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AX2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AY2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="BA2" s="4">
+        <f t="shared" si="0"/>
+        <v>50539.834620237118</v>
+      </c>
+      <c r="BB2" s="4">
+        <f t="shared" si="0"/>
         <v>50539.834620237118</v>
       </c>
     </row>
@@ -2119,21 +2385,21 @@
     <tabColor rgb="FF1F497D"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="4">
         <f>ROUND('Data and Calculations'!A22,0)</f>
         <v>4</v>
       </c>
@@ -2144,21 +2410,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -2302,14 +2553,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD124F93-4C1F-4E6F-9FF6-BBDFC587A76D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EC3B175-1A50-44DD-A6FF-610DA475B8B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC1EE97F-BEF3-4E27-B60F-7AF2FDABE2B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC1EE97F-BEF3-4E27-B60F-7AF2FDABE2B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EC3B175-1A50-44DD-A6FF-610DA475B8B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD124F93-4C1F-4E6F-9FF6-BBDFC587A76D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>